--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc6e1003b337f47a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13e9ce562d7e437c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rc74e59315953467d" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R5c3a053053434020" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13e9ce562d7e437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9b50ad6bc0b4d33"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R5c3a053053434020" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R0dd7f312d42e45fe" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf9b50ad6bc0b4d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R67665c13fccd4dec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R0dd7f312d42e45fe" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R3171bd6db71f4d3d" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R67665c13fccd4dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ebef6988c364cd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R3171bd6db71f4d3d" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd74655504f95451f" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ebef6988c364cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R29363bfc180d44f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd74655504f95451f" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R2ee4339ded6b4a3c" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R29363bfc180d44f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0920515175849b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R2ee4339ded6b4a3c" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Re1abb4f9109c4762" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc0920515175849b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c0a59ff3f324f44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Re1abb4f9109c4762" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R37cac3afafa949aa" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c0a59ff3f324f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc52d0b1890364a5c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R37cac3afafa949aa" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rcf9d9b291ab74398" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc52d0b1890364a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb4527f6283bd41a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rcf9d9b291ab74398" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd2c50d52851d4f0a" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb4527f6283bd41a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R55c9bb24f8ea41cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd2c50d52851d4f0a" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R112d5bcfed8d4d93" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>